--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488054_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488054_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>14.5134</v>
+        <v>12.6661</v>
       </c>
       <c r="E2" t="n">
-        <v>9.865500000000001</v>
+        <v>8.439299999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>4.6479</v>
+        <v>4.2267</v>
       </c>
       <c r="G2" t="n">
         <v>4.8387</v>
@@ -610,13 +610,13 @@
         <v>2.5769</v>
       </c>
       <c r="S2" t="n">
-        <v>4.6638</v>
+        <v>2.8164</v>
       </c>
       <c r="T2" t="n">
-        <v>3.7114</v>
+        <v>2.2853</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9523</v>
+        <v>0.5312</v>
       </c>
       <c r="V2" t="n">
         <v>3.4252</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. RUEDA SANTAELLA</t>
+          <t>E. DOMENECH ANTE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>10.6298</v>
+        <v>11.3771</v>
       </c>
       <c r="E3" t="n">
-        <v>7.5724</v>
+        <v>5.8058</v>
       </c>
       <c r="F3" t="n">
-        <v>3.0575</v>
+        <v>5.5713</v>
       </c>
       <c r="G3" t="n">
-        <v>6.1197</v>
+        <v>5.9173</v>
       </c>
       <c r="H3" t="n">
-        <v>4.1684</v>
+        <v>4.2452</v>
       </c>
       <c r="I3" t="n">
-        <v>1.9513</v>
+        <v>1.6722</v>
       </c>
       <c r="J3" t="n">
-        <v>6.4149</v>
+        <v>4.4621</v>
       </c>
       <c r="K3" t="n">
-        <v>5.1655</v>
+        <v>4.5671</v>
       </c>
       <c r="L3" t="n">
-        <v>1.2494</v>
+        <v>-0.105</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2952</v>
+        <v>1.4552</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9971</v>
+        <v>-0.3219</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7019</v>
+        <v>1.7771</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9911</v>
+        <v>0.7929</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R3" t="n">
-        <v>1.9822</v>
+        <v>2.7751</v>
       </c>
       <c r="S3" t="n">
-        <v>1.7788</v>
+        <v>2.1823</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7453</v>
+        <v>1.5153</v>
       </c>
       <c r="U3" t="n">
-        <v>1.0335</v>
+        <v>0.667</v>
       </c>
       <c r="V3" t="n">
-        <v>1.7403</v>
+        <v>2.4846</v>
       </c>
       <c r="W3" t="n">
-        <v>1.4033</v>
+        <v>1.8107</v>
       </c>
       <c r="X3" t="n">
-        <v>0.337</v>
+        <v>0.674</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. DOMENECH ANTE</t>
+          <t>L. RUEDA SANTAELLA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>9.6753</v>
+        <v>10.9728</v>
       </c>
       <c r="E4" t="n">
-        <v>4.3567</v>
+        <v>8.308400000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>5.3186</v>
+        <v>2.6644</v>
       </c>
       <c r="G4" t="n">
-        <v>5.9173</v>
+        <v>6.1197</v>
       </c>
       <c r="H4" t="n">
-        <v>4.2452</v>
+        <v>4.1684</v>
       </c>
       <c r="I4" t="n">
-        <v>1.6722</v>
+        <v>1.9513</v>
       </c>
       <c r="J4" t="n">
-        <v>4.4621</v>
+        <v>6.4149</v>
       </c>
       <c r="K4" t="n">
-        <v>4.5671</v>
+        <v>5.1655</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.105</v>
+        <v>1.2494</v>
       </c>
       <c r="M4" t="n">
-        <v>1.4552</v>
+        <v>-0.2952</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3219</v>
+        <v>-0.9971</v>
       </c>
       <c r="O4" t="n">
-        <v>1.7771</v>
+        <v>0.7019</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7929</v>
+        <v>0.9911</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R4" t="n">
-        <v>2.7751</v>
+        <v>1.9822</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4805</v>
+        <v>2.1217</v>
       </c>
       <c r="T4" t="n">
-        <v>0.06619999999999999</v>
+        <v>1.4813</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4143</v>
+        <v>0.6403</v>
       </c>
       <c r="V4" t="n">
-        <v>2.4846</v>
+        <v>1.7403</v>
       </c>
       <c r="W4" t="n">
-        <v>1.8107</v>
+        <v>1.4033</v>
       </c>
       <c r="X4" t="n">
-        <v>0.674</v>
+        <v>0.337</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.6831</v>
+        <v>2.735</v>
       </c>
       <c r="E5" t="n">
-        <v>2.4687</v>
+        <v>1.8575</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2144</v>
+        <v>0.8774</v>
       </c>
       <c r="G5" t="n">
         <v>1.2076</v>
@@ -844,13 +844,13 @@
         <v>1.5858</v>
       </c>
       <c r="S5" t="n">
-        <v>1.9007</v>
+        <v>0.9525</v>
       </c>
       <c r="T5" t="n">
-        <v>1.039</v>
+        <v>0.4278</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8616</v>
+        <v>0.5247000000000001</v>
       </c>
       <c r="V5" t="n">
         <v>-1.0109</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. BELEMENE DZABATOU</t>
+          <t>C. ZULUAGA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.1709</v>
+        <v>1.335</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8028</v>
+        <v>-0.9395</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3681</v>
+        <v>2.2745</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1904</v>
+        <v>0.3381</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.0743</v>
+        <v>-3.0291</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8839</v>
+        <v>3.3671</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.7511</v>
+        <v>0.1616</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6786</v>
+        <v>-1.6944</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.0726</v>
+        <v>1.856</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5608</v>
+        <v>0.1765</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3957</v>
+        <v>-1.3347</v>
       </c>
       <c r="O6" t="n">
-        <v>0.9565</v>
+        <v>1.5112</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.5858</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.9733</v>
+        <v>-1.9822</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3876</v>
+        <v>1.5858</v>
       </c>
       <c r="S6" t="n">
-        <v>5.0174</v>
+        <v>0.7195</v>
       </c>
       <c r="T6" t="n">
-        <v>4.3906</v>
+        <v>0.8811</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6269</v>
+        <v>-0.1617</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.0704</v>
+        <v>0.674</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1367</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2071</v>
+        <v>0.674</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. TORRECILLAS  LAJARA</t>
+          <t>C. BELEMENE DZABATOU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6027</v>
+        <v>1.1002</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6027</v>
+        <v>-0.2117</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1.3119</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6027</v>
+        <v>-0.1904</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>-1.0743</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6027</v>
+        <v>0.8839</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6027</v>
+        <v>-0.7511</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>-0.6786</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6027</v>
+        <v>-0.0726</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>0.5608</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-0.3957</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.9565</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-1.5858</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.9733</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.3876</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.9468</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.3761</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.5707</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.0704</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.1367</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. ZULUAGA</t>
+          <t>S. TORRECILLAS  LAJARA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0415</v>
+        <v>0.6027</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7545</v>
+        <v>0.6027</v>
       </c>
       <c r="F8" t="n">
-        <v>1.713</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3381</v>
+        <v>0.6027</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.0291</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>3.3671</v>
+        <v>0.6027</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1616</v>
+        <v>0.6027</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.6944</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1.856</v>
+        <v>0.6027</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1765</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.3347</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1.5112</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3964</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5858</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6571</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.06619999999999999</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7233000000000001</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>0.674</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.674</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2293</v>
+        <v>-0.5971</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6183999999999999</v>
+        <v>-0.2109</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6108</v>
+        <v>-0.3862</v>
       </c>
       <c r="G9" t="n">
         <v>-0.0589</v>
@@ -1156,13 +1156,13 @@
         <v>0.7929</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7055</v>
+        <v>-0.07340000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.624</v>
+        <v>-0.2165</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.08160000000000001</v>
+        <v>0.1431</v>
       </c>
       <c r="V9" t="n">
         <v>-0.2666</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3748</v>
+        <v>-1.6668</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.9854</v>
+        <v>-4.2494</v>
       </c>
       <c r="F10" t="n">
-        <v>2.6107</v>
+        <v>2.5826</v>
       </c>
       <c r="G10" t="n">
         <v>-2.0735</v>
@@ -1234,13 +1234,13 @@
         <v>2.1805</v>
       </c>
       <c r="S10" t="n">
-        <v>0.899</v>
+        <v>1.6069</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1103</v>
+        <v>0.8463000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>0.7887</v>
+        <v>0.7606000000000001</v>
       </c>
       <c r="V10" t="n">
         <v>-0.4074</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.1678</v>
+        <v>-2.6833</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2197</v>
+        <v>-2.0159</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9481000000000001</v>
+        <v>-0.6674</v>
       </c>
       <c r="G11" t="n">
         <v>-1.4403</v>
@@ -1312,13 +1312,13 @@
         <v>0.3964</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8663</v>
+        <v>-0.3818</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3744</v>
+        <v>-0.1706</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4919</v>
+        <v>-0.2112</v>
       </c>
       <c r="V11" t="n">
         <v>-0.2666</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.8629</v>
+        <v>-6.6186</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.3796</v>
+        <v>-6.0511</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4833</v>
+        <v>-0.5676</v>
       </c>
       <c r="G12" t="n">
         <v>-5.19</v>
@@ -1390,13 +1390,13 @@
         <v>0.5947</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3182</v>
+        <v>0.5625</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3192</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6375</v>
+        <v>0.5532</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6036</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>28.5989</v>
+        <v>29.2231</v>
       </c>
       <c r="E13" t="n">
-        <v>10.7112</v>
+        <v>11.3352</v>
       </c>
       <c r="F13" t="n">
-        <v>17.888</v>
+        <v>17.8876</v>
       </c>
       <c r="G13" t="n">
         <v>10.071</v>
@@ -1456,7 +1456,7 @@
         <v>-10.3204</v>
       </c>
       <c r="O13" t="n">
-        <v>9.650400000000001</v>
+        <v>9.650399999999999</v>
       </c>
       <c r="P13" t="n">
         <v>4.440892098500626e-16</v>
@@ -1468,13 +1468,13 @@
         <v>15.8579</v>
       </c>
       <c r="S13" t="n">
-        <v>12.8295</v>
+        <v>13.4534</v>
       </c>
       <c r="T13" t="n">
-        <v>8.811400000000001</v>
+        <v>9.435399999999998</v>
       </c>
       <c r="U13" t="n">
-        <v>4.018000000000001</v>
+        <v>4.017900000000001</v>
       </c>
       <c r="V13" t="n">
         <v>5.698599999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8821</v>
+        <v>0.3414</v>
       </c>
       <c r="E14" t="n">
-        <v>1.6314</v>
+        <v>1.4277</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.7493</v>
+        <v>-1.0863</v>
       </c>
       <c r="G14" t="n">
         <v>2.1878</v>
@@ -1546,13 +1546,13 @@
         <v>1.1893</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.0213</v>
+        <v>-1.562</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.444</v>
+        <v>-0.6478</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5773</v>
+        <v>-0.9142</v>
       </c>
       <c r="V14" t="n">
         <v>-1.4737</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.3553</v>
+        <v>-0.1691</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.3771</v>
+        <v>-2.2752</v>
       </c>
       <c r="F15" t="n">
-        <v>2.0218</v>
+        <v>2.106</v>
       </c>
       <c r="G15" t="n">
         <v>-2.1701</v>
@@ -1624,13 +1624,13 @@
         <v>1.784</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2558</v>
+        <v>-0.0697</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3816</v>
+        <v>-0.2798</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1258</v>
+        <v>0.21</v>
       </c>
       <c r="V15" t="n">
         <v>0.2867</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. JIMENEZ HERRERA</t>
+          <t>T. ESTEVES VEHVILAINEN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.9002</v>
+        <v>-1.3596</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2964</v>
+        <v>0.2412</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6038</v>
+        <v>-1.6008</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.4831</v>
+        <v>-2.339</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.2426</v>
+        <v>-1.9813</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7595</v>
+        <v>-0.3577</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.2892</v>
+        <v>-0.1619</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.3696</v>
+        <v>0.6261</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0804</v>
+        <v>-0.788</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1939</v>
+        <v>-2.1771</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8731</v>
+        <v>-2.6074</v>
       </c>
       <c r="O16" t="n">
-        <v>0.6791</v>
+        <v>0.4303</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.1982</v>
+        <v>0.9911</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R16" t="n">
-        <v>0.7929</v>
+        <v>1.9822</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6513</v>
+        <v>-2.1593</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9839</v>
+        <v>-0.4164</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3326</v>
+        <v>-1.7429</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.8701</v>
+        <v>2.1476</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.8107</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.8701</v>
+        <v>0.337</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T. ESTEVES VEHVILAINEN</t>
+          <t>J. JIMENEZ HERRERA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.5588</v>
+        <v>-1.3651</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0374</v>
+        <v>-1.0095</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.5962</v>
+        <v>-0.3556</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.339</v>
+        <v>-0.4831</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.9813</v>
+        <v>-1.2426</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3577</v>
+        <v>0.7595</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1619</v>
+        <v>-0.2892</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6261</v>
+        <v>-0.3696</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.788</v>
+        <v>0.0804</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.1771</v>
+        <v>-0.1939</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.6074</v>
+        <v>-0.8731</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4303</v>
+        <v>0.6791</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9911</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9822</v>
+        <v>0.7929</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.3585</v>
+        <v>0.1863</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6202</v>
+        <v>0.2708</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.7383</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>2.1476</v>
+        <v>-0.8701</v>
       </c>
       <c r="W17" t="n">
-        <v>1.8107</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.337</v>
+        <v>-0.8701</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.6533</v>
+        <v>-2.569</v>
       </c>
       <c r="E18" t="n">
         <v>0.029</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.6823</v>
+        <v>-2.598</v>
       </c>
       <c r="G18" t="n">
         <v>0.7965</v>
@@ -1858,13 +1858,13 @@
         <v>2.3787</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8284</v>
+        <v>-0.7442</v>
       </c>
       <c r="T18" t="n">
         <v>-0.3706</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4578</v>
+        <v>-0.3736</v>
       </c>
       <c r="V18" t="n">
         <v>-3.0178</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.6166</v>
+        <v>-3.6342</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.6355</v>
+        <v>-3.7374</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0189</v>
+        <v>0.1031</v>
       </c>
       <c r="G19" t="n">
         <v>-1.4897</v>
@@ -1936,13 +1936,13 @@
         <v>1.1893</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9974</v>
+        <v>-1.015</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.444</v>
+        <v>-0.5459000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5533</v>
+        <v>-0.4691</v>
       </c>
       <c r="V19" t="n">
         <v>-1.3278</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.1374</v>
+        <v>-3.6751</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6364</v>
+        <v>-1.5345</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.501</v>
+        <v>-2.1406</v>
       </c>
       <c r="G20" t="n">
         <v>-1.4853</v>
@@ -2014,13 +2014,13 @@
         <v>1.5858</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.8639</v>
+        <v>-2.4016</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.745</v>
+        <v>-0.6431</v>
       </c>
       <c r="U20" t="n">
-        <v>-2.119</v>
+        <v>-1.7585</v>
       </c>
       <c r="V20" t="n">
         <v>1.5994</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.4169</v>
+        <v>-3.9859</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.1802</v>
+        <v>-1.7727</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.2367</v>
+        <v>-2.2132</v>
       </c>
       <c r="G21" t="n">
         <v>-2.49</v>
@@ -2092,13 +2092,13 @@
         <v>1.5858</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2642</v>
+        <v>-0.8332000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8074</v>
+        <v>-0.3999</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4568</v>
+        <v>-0.4333</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2574</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.2141</v>
+        <v>-4.7374</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.2302</v>
+        <v>-2.7208</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.9839</v>
+        <v>-2.0166</v>
       </c>
       <c r="G22" t="n">
         <v>-0.4254</v>
@@ -2170,13 +2170,13 @@
         <v>0.9911</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.8068</v>
+        <v>-2.3301</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.1855</v>
+        <v>-0.6762</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.6212</v>
+        <v>-1.6539</v>
       </c>
       <c r="V22" t="n">
         <v>-0.9908</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.6285</v>
+        <v>-6.7657</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.23</v>
+        <v>-6.5356</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3986</v>
+        <v>-0.2301</v>
       </c>
       <c r="G23" t="n">
         <v>-2.1727</v>
@@ -2248,13 +2248,13 @@
         <v>2.3787</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0843</v>
+        <v>-1.2214</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0034</v>
+        <v>-0.3091</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.0808</v>
+        <v>-0.9123</v>
       </c>
       <c r="V23" t="n">
         <v>-0.7947</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-28.599</v>
+        <v>-27.9197</v>
       </c>
       <c r="E24" t="n">
-        <v>-17.888</v>
+        <v>-17.8878</v>
       </c>
       <c r="F24" t="n">
-        <v>-10.7111</v>
+        <v>-10.0321</v>
       </c>
       <c r="G24" t="n">
         <v>-10.071</v>
@@ -2326,13 +2326,13 @@
         <v>15.8578</v>
       </c>
       <c r="S24" t="n">
-        <v>-12.8293</v>
+        <v>-12.1502</v>
       </c>
       <c r="T24" t="n">
-        <v>-4.0178</v>
+        <v>-4.018000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>-8.811299999999999</v>
+        <v>-8.132299999999999</v>
       </c>
       <c r="V24" t="n">
         <v>-5.6986</v>
